--- a/AMS/005-Kittypark/Kitty Park Draft Financial _25-26_V1.xlsx
+++ b/AMS/005-Kittypark/Kitty Park Draft Financial _25-26_V1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BHARAT\2025-2026\BCB\AMS\005-Kittypark\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25DEB99F-0742-4296-907B-CCBF3F88FD43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88A83E47-054A-4D29-B9E1-98DB2BB5D7F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="702" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="702" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BS" sheetId="2" r:id="rId1"/>
@@ -1992,7 +1992,7 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="251">
+  <cellXfs count="247">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -2315,26 +2315,50 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="2" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="30" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="32" fillId="0" borderId="22" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2342,73 +2366,16 @@
     <xf numFmtId="168" fontId="32" fillId="0" borderId="20" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2444,6 +2411,12 @@
     <xf numFmtId="43" fontId="9" fillId="0" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="43" fontId="10" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2462,17 +2435,110 @@
     <xf numFmtId="43" fontId="6" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2486,78 +2552,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="2" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="30" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -2844,70 +2838,67 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
   <dimension ref="A1:J76"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+    <col min="1" max="1" width="14.77734375" customWidth="1"/>
     <col min="2" max="2" width="41.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.77734375" customWidth="1"/>
     <col min="6" max="6" width="33.109375" customWidth="1"/>
     <col min="7" max="7" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.6640625" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" customWidth="1"/>
     <col min="9" max="9" width="14.44140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A1" s="173" t="s">
+      <c r="A1" s="209" t="s">
         <v>133</v>
       </c>
-      <c r="B1" s="174"/>
-      <c r="C1" s="174"/>
-      <c r="D1" s="174"/>
-      <c r="E1" s="174"/>
-      <c r="F1" s="174"/>
-      <c r="G1" s="174"/>
-      <c r="H1" s="175"/>
+      <c r="B1" s="210"/>
+      <c r="C1" s="210"/>
+      <c r="D1" s="210"/>
+      <c r="E1" s="210"/>
+      <c r="F1" s="210"/>
+      <c r="G1" s="210"/>
+      <c r="H1" s="211"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="176" t="s">
+      <c r="A2" s="212" t="s">
         <v>149</v>
       </c>
-      <c r="B2" s="177"/>
-      <c r="C2" s="177"/>
-      <c r="D2" s="177"/>
-      <c r="E2" s="177"/>
-      <c r="F2" s="177"/>
-      <c r="G2" s="177"/>
-      <c r="H2" s="178"/>
+      <c r="B2" s="213"/>
+      <c r="C2" s="213"/>
+      <c r="D2" s="213"/>
+      <c r="E2" s="213"/>
+      <c r="F2" s="213"/>
+      <c r="G2" s="213"/>
+      <c r="H2" s="214"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="191" t="s">
+      <c r="A3" s="206" t="s">
         <v>186</v>
       </c>
-      <c r="B3" s="192"/>
-      <c r="C3" s="192"/>
-      <c r="D3" s="192"/>
-      <c r="E3" s="192"/>
-      <c r="F3" s="192"/>
-      <c r="G3" s="192"/>
-      <c r="H3" s="193"/>
+      <c r="B3" s="207"/>
+      <c r="C3" s="207"/>
+      <c r="D3" s="207"/>
+      <c r="E3" s="207"/>
+      <c r="F3" s="207"/>
+      <c r="G3" s="207"/>
+      <c r="H3" s="208"/>
     </row>
     <row r="4" spans="1:9" ht="18" x14ac:dyDescent="0.35">
-      <c r="A4" s="183" t="s">
+      <c r="A4" s="221" t="s">
         <v>291</v>
       </c>
-      <c r="B4" s="184"/>
-      <c r="C4" s="184"/>
-      <c r="D4" s="184"/>
-      <c r="E4" s="184"/>
-      <c r="F4" s="184"/>
-      <c r="G4" s="184"/>
-      <c r="H4" s="185"/>
+      <c r="B4" s="222"/>
+      <c r="C4" s="222"/>
+      <c r="D4" s="222"/>
+      <c r="E4" s="222"/>
+      <c r="F4" s="222"/>
+      <c r="G4" s="222"/>
+      <c r="H4" s="223"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="146"/>
@@ -2922,46 +2913,46 @@
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="223" t="s">
+      <c r="A6" s="226" t="s">
         <v>289</v>
       </c>
-      <c r="B6" s="224" t="s">
+      <c r="B6" s="215" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="225"/>
-      <c r="D6" s="226" t="s">
+      <c r="C6" s="216"/>
+      <c r="D6" s="230" t="s">
         <v>290</v>
       </c>
-      <c r="E6" s="189" t="str">
+      <c r="E6" s="228" t="str">
         <f>A6</f>
         <v>Previous Year 2024-25</v>
       </c>
-      <c r="F6" s="179" t="s">
+      <c r="F6" s="219" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="180"/>
-      <c r="H6" s="189" t="str">
+      <c r="G6" s="220"/>
+      <c r="H6" s="228" t="str">
         <f>D6</f>
         <v>Current Year 2025-26</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="188"/>
-      <c r="B7" s="181"/>
-      <c r="C7" s="182"/>
-      <c r="D7" s="227"/>
-      <c r="E7" s="190"/>
-      <c r="F7" s="181"/>
-      <c r="G7" s="182"/>
-      <c r="H7" s="190"/>
+      <c r="A7" s="227"/>
+      <c r="B7" s="217"/>
+      <c r="C7" s="218"/>
+      <c r="D7" s="231"/>
+      <c r="E7" s="229"/>
+      <c r="F7" s="217"/>
+      <c r="G7" s="218"/>
+      <c r="H7" s="229"/>
     </row>
     <row r="8" spans="1:9" ht="17.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A8" s="149"/>
-      <c r="B8" s="228" t="s">
+      <c r="B8" s="85" t="s">
         <v>19</v>
       </c>
       <c r="C8" s="31"/>
-      <c r="D8" s="229"/>
+      <c r="D8" s="164"/>
       <c r="E8" s="31"/>
       <c r="F8" s="150" t="s">
         <v>178</v>
@@ -2973,11 +2964,11 @@
       <c r="A9" s="151">
         <v>10000</v>
       </c>
-      <c r="B9" s="230" t="s">
+      <c r="B9" s="10" t="s">
         <v>134</v>
       </c>
       <c r="C9" s="31"/>
-      <c r="D9" s="231">
+      <c r="D9" s="165">
         <v>10000</v>
       </c>
       <c r="E9" s="31">
@@ -2995,7 +2986,7 @@
       <c r="A10" s="149"/>
       <c r="B10" s="86"/>
       <c r="C10" s="31"/>
-      <c r="D10" s="229"/>
+      <c r="D10" s="164"/>
       <c r="E10" s="31">
         <v>95191.48</v>
       </c>
@@ -3011,11 +3002,11 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="149"/>
-      <c r="B11" s="232" t="s">
+      <c r="B11" s="150" t="s">
         <v>158</v>
       </c>
       <c r="C11" s="31"/>
-      <c r="D11" s="229"/>
+      <c r="D11" s="164"/>
       <c r="E11" s="31">
         <v>316931.84999999998</v>
       </c>
@@ -3039,7 +3030,7 @@
         <v>168</v>
       </c>
       <c r="C12" s="31"/>
-      <c r="D12" s="229">
+      <c r="D12" s="164">
         <v>6500</v>
       </c>
       <c r="E12" s="31"/>
@@ -3050,7 +3041,7 @@
       <c r="A13" s="149"/>
       <c r="B13" s="86"/>
       <c r="C13" s="31"/>
-      <c r="D13" s="229"/>
+      <c r="D13" s="164"/>
       <c r="E13" s="31"/>
       <c r="F13" s="150" t="s">
         <v>207</v>
@@ -3060,11 +3051,11 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="149"/>
-      <c r="B14" s="232" t="s">
+      <c r="B14" s="150" t="s">
         <v>136</v>
       </c>
       <c r="C14" s="31"/>
-      <c r="D14" s="229"/>
+      <c r="D14" s="164"/>
       <c r="E14" s="31">
         <v>1430092</v>
       </c>
@@ -3079,11 +3070,11 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="149"/>
-      <c r="B15" s="232" t="s">
+      <c r="B15" s="150" t="s">
         <v>182</v>
       </c>
       <c r="C15" s="31"/>
-      <c r="D15" s="229"/>
+      <c r="D15" s="164"/>
       <c r="E15" s="31">
         <v>93181</v>
       </c>
@@ -3110,7 +3101,7 @@
         <f>SUM(A16:A18)</f>
         <v>310812</v>
       </c>
-      <c r="D16" s="229"/>
+      <c r="D16" s="164"/>
       <c r="E16" s="31"/>
       <c r="G16" s="31"/>
       <c r="H16" s="91"/>
@@ -3125,7 +3116,7 @@
       <c r="C17" s="31">
         <v>0</v>
       </c>
-      <c r="D17" s="229"/>
+      <c r="D17" s="164"/>
       <c r="E17" s="31"/>
       <c r="F17" s="150" t="s">
         <v>176</v>
@@ -3144,7 +3135,7 @@
         <f>'FD Interest Working'!D58</f>
         <v>19964</v>
       </c>
-      <c r="D18" s="229">
+      <c r="D18" s="164">
         <f>SUM(C16:C18)</f>
         <v>330776</v>
       </c>
@@ -3161,11 +3152,11 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="149"/>
-      <c r="B19" s="232" t="s">
+      <c r="B19" s="150" t="s">
         <v>183</v>
       </c>
       <c r="C19" s="31"/>
-      <c r="D19" s="229"/>
+      <c r="D19" s="164"/>
       <c r="E19" s="31"/>
       <c r="G19" s="31"/>
       <c r="H19" s="91"/>
@@ -3181,7 +3172,7 @@
         <f>SUM(A20:A22)</f>
         <v>150488</v>
       </c>
-      <c r="D20" s="229"/>
+      <c r="D20" s="164"/>
       <c r="E20" s="31"/>
       <c r="F20" s="150" t="s">
         <v>177</v>
@@ -3199,7 +3190,7 @@
       <c r="C21" s="31">
         <v>2520</v>
       </c>
-      <c r="D21" s="229"/>
+      <c r="D21" s="164"/>
       <c r="E21" s="31">
         <v>5365</v>
       </c>
@@ -3222,7 +3213,7 @@
         <f>'FD Interest Working'!D60</f>
         <v>11206</v>
       </c>
-      <c r="D22" s="229">
+      <c r="D22" s="164">
         <f>SUM(C20:C22)</f>
         <v>164214</v>
       </c>
@@ -3233,11 +3224,11 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="149"/>
-      <c r="B23" s="232" t="s">
+      <c r="B23" s="150" t="s">
         <v>184</v>
       </c>
       <c r="C23" s="31"/>
-      <c r="D23" s="229"/>
+      <c r="D23" s="164"/>
       <c r="E23" s="31">
         <v>29459</v>
       </c>
@@ -3261,7 +3252,7 @@
         <f>SUM(A24:A26)</f>
         <v>538462</v>
       </c>
-      <c r="D24" s="229"/>
+      <c r="D24" s="164"/>
       <c r="E24" s="31"/>
       <c r="F24" s="86"/>
       <c r="G24" s="31"/>
@@ -3277,7 +3268,7 @@
       <c r="C25" s="31">
         <v>7440</v>
       </c>
-      <c r="D25" s="229"/>
+      <c r="D25" s="164"/>
       <c r="E25" s="31">
         <v>66500</v>
       </c>
@@ -3301,7 +3292,7 @@
         <f>'FD Interest Working'!D56</f>
         <v>41764</v>
       </c>
-      <c r="D26" s="229">
+      <c r="D26" s="164">
         <f>SUM(C24:C26)</f>
         <v>587666</v>
       </c>
@@ -3311,11 +3302,11 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="149"/>
-      <c r="B27" s="232" t="s">
+      <c r="B27" s="150" t="s">
         <v>185</v>
       </c>
       <c r="C27" s="31"/>
-      <c r="D27" s="229"/>
+      <c r="D27" s="164"/>
       <c r="E27" s="31"/>
       <c r="G27" s="31"/>
       <c r="H27" s="91"/>
@@ -3331,7 +3322,7 @@
         <f>SUM(A28:A31)</f>
         <v>0</v>
       </c>
-      <c r="D28" s="229"/>
+      <c r="D28" s="164"/>
       <c r="E28" s="31"/>
       <c r="F28" s="150" t="s">
         <v>175</v>
@@ -3349,7 +3340,7 @@
       <c r="C29" s="31">
         <v>31200</v>
       </c>
-      <c r="D29" s="229"/>
+      <c r="D29" s="164"/>
       <c r="E29" s="31">
         <v>11031100</v>
       </c>
@@ -3374,7 +3365,7 @@
         <f>'FD Interest Working'!D57</f>
         <v>32376</v>
       </c>
-      <c r="D30" s="229"/>
+      <c r="D30" s="164"/>
       <c r="E30" s="31"/>
       <c r="G30" s="31"/>
       <c r="H30" s="91"/>
@@ -3389,7 +3380,7 @@
       <c r="C31" s="89">
         <v>0</v>
       </c>
-      <c r="D31" s="229">
+      <c r="D31" s="164">
         <f>SUM(C28:C31)</f>
         <v>63576</v>
       </c>
@@ -3410,14 +3401,14 @@
         <v>255</v>
       </c>
       <c r="C32" s="31"/>
-      <c r="D32" s="229"/>
+      <c r="D32" s="164"/>
       <c r="E32" s="31">
         <v>-407</v>
       </c>
       <c r="F32" t="s">
         <v>164</v>
       </c>
-      <c r="G32" s="250">
+      <c r="G32" s="180">
         <f>-ROUND(G31*15%,0)</f>
         <v>-346</v>
       </c>
@@ -3437,7 +3428,7 @@
         <f>SUM(A33:A36)</f>
         <v>347977</v>
       </c>
-      <c r="D33" s="229"/>
+      <c r="D33" s="164"/>
       <c r="E33" s="31"/>
       <c r="G33" s="31"/>
       <c r="H33" s="91"/>
@@ -3452,7 +3443,7 @@
       <c r="C34" s="31">
         <v>0</v>
       </c>
-      <c r="D34" s="229"/>
+      <c r="D34" s="164"/>
       <c r="E34" s="31">
         <v>493</v>
       </c>
@@ -3474,14 +3465,14 @@
       <c r="C35" s="31">
         <v>195000</v>
       </c>
-      <c r="D35" s="229"/>
+      <c r="D35" s="164"/>
       <c r="E35" s="31">
         <v>-49</v>
       </c>
       <c r="F35" t="s">
         <v>165</v>
       </c>
-      <c r="G35" s="250">
+      <c r="G35" s="180">
         <f>-ROUND(G34*10%,0)</f>
         <v>-44</v>
       </c>
@@ -3497,10 +3488,10 @@
       <c r="B36" s="86" t="s">
         <v>257</v>
       </c>
-      <c r="C36" s="250">
+      <c r="C36" s="180">
         <v>-234625</v>
       </c>
-      <c r="D36" s="229">
+      <c r="D36" s="164">
         <f>SUM(C33:C36)</f>
         <v>308352</v>
       </c>
@@ -3512,14 +3503,14 @@
       <c r="A37" s="149">
         <v>13986</v>
       </c>
-      <c r="B37" s="232" t="s">
+      <c r="B37" s="150" t="s">
         <v>258</v>
       </c>
       <c r="C37" s="31">
         <f>SUM(A37:A39)</f>
         <v>16621</v>
       </c>
-      <c r="D37" s="229"/>
+      <c r="D37" s="164"/>
       <c r="E37" s="31">
         <v>5076</v>
       </c>
@@ -3541,14 +3532,14 @@
       <c r="C38" s="31">
         <v>1560</v>
       </c>
-      <c r="D38" s="229"/>
+      <c r="D38" s="164"/>
       <c r="E38" s="31">
         <v>-761</v>
       </c>
       <c r="F38" t="s">
         <v>164</v>
       </c>
-      <c r="G38" s="250">
+      <c r="G38" s="180">
         <f>-ROUND(G37*15%,0)</f>
         <v>-647</v>
       </c>
@@ -3568,7 +3559,7 @@
         <f>'FD Interest Working'!D55</f>
         <v>1092</v>
       </c>
-      <c r="D39" s="229">
+      <c r="D39" s="164">
         <f>SUM(C37:C39)</f>
         <v>19273</v>
       </c>
@@ -3580,7 +3571,7 @@
       <c r="A40" s="149"/>
       <c r="B40" s="86"/>
       <c r="C40" s="31"/>
-      <c r="D40" s="229"/>
+      <c r="D40" s="164"/>
       <c r="E40" s="31">
         <v>18777</v>
       </c>
@@ -3595,18 +3586,18 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="149"/>
-      <c r="B41" s="232" t="s">
+      <c r="B41" s="150" t="s">
         <v>171</v>
       </c>
       <c r="C41" s="31"/>
-      <c r="D41" s="229"/>
+      <c r="D41" s="164"/>
       <c r="E41" s="31">
         <v>-2817</v>
       </c>
       <c r="F41" t="s">
         <v>164</v>
       </c>
-      <c r="G41" s="250">
+      <c r="G41" s="180">
         <f>-ROUND(G40*15%,0)</f>
         <v>-2394</v>
       </c>
@@ -3623,7 +3614,7 @@
         <v>170</v>
       </c>
       <c r="C42" s="91"/>
-      <c r="D42" s="229">
+      <c r="D42" s="164">
         <v>11031100</v>
       </c>
       <c r="E42" s="31"/>
@@ -3634,7 +3625,7 @@
       <c r="A43" s="149"/>
       <c r="B43" s="86"/>
       <c r="C43" s="31"/>
-      <c r="D43" s="229"/>
+      <c r="D43" s="164"/>
       <c r="E43" s="31"/>
       <c r="F43" s="85" t="s">
         <v>415</v>
@@ -3644,11 +3635,11 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="149"/>
-      <c r="B44" s="232" t="s">
+      <c r="B44" s="150" t="s">
         <v>173</v>
       </c>
       <c r="C44" s="31"/>
-      <c r="D44" s="229"/>
+      <c r="D44" s="164"/>
       <c r="E44" s="31">
         <v>0</v>
       </c>
@@ -3675,7 +3666,7 @@
         <f>'SCH-II-III-IV-V'!D13</f>
         <v>78327</v>
       </c>
-      <c r="D45" s="229"/>
+      <c r="D45" s="164"/>
       <c r="E45" s="31"/>
       <c r="G45" s="31"/>
       <c r="H45" s="91"/>
@@ -3691,7 +3682,7 @@
         <f>'Vendor Prov n Advance'!D18</f>
         <v>36814</v>
       </c>
-      <c r="D46" s="229"/>
+      <c r="D46" s="164"/>
       <c r="E46" s="31"/>
       <c r="G46" s="31"/>
       <c r="H46" s="91"/>
@@ -3706,7 +3697,7 @@
       <c r="C47" s="31">
         <v>1300</v>
       </c>
-      <c r="D47" s="229"/>
+      <c r="D47" s="164"/>
       <c r="E47" s="31"/>
       <c r="F47" s="85" t="s">
         <v>174</v>
@@ -3725,7 +3716,7 @@
       <c r="C48" s="31">
         <v>4803</v>
       </c>
-      <c r="D48" s="229"/>
+      <c r="D48" s="164"/>
       <c r="E48" s="31"/>
       <c r="G48" s="31"/>
       <c r="H48" s="91"/>
@@ -3741,7 +3732,7 @@
       <c r="C49" s="31">
         <v>37125</v>
       </c>
-      <c r="D49" s="229">
+      <c r="D49" s="164">
         <f>SUM(C45:C49)</f>
         <v>158369</v>
       </c>
@@ -3759,9 +3750,8 @@
     </row>
     <row r="50" spans="1:10" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="149"/>
-      <c r="B50" s="233"/>
       <c r="C50" s="31"/>
-      <c r="D50" s="229"/>
+      <c r="D50" s="164"/>
       <c r="E50" s="31">
         <v>0</v>
       </c>
@@ -3777,11 +3767,11 @@
     </row>
     <row r="51" spans="1:10" s="25" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="149"/>
-      <c r="B51" s="232" t="s">
+      <c r="B51" s="150" t="s">
         <v>172</v>
       </c>
       <c r="C51" s="31"/>
-      <c r="D51" s="229"/>
+      <c r="D51" s="164"/>
       <c r="E51" s="31"/>
       <c r="F51"/>
       <c r="G51" s="31"/>
@@ -3798,7 +3788,7 @@
         <f>SUM(A52:A54)</f>
         <v>296659.32999999996</v>
       </c>
-      <c r="D52" s="229"/>
+      <c r="D52" s="164"/>
       <c r="E52" s="31"/>
       <c r="F52"/>
       <c r="G52" s="31"/>
@@ -3811,11 +3801,11 @@
       <c r="B53" s="93" t="s">
         <v>208</v>
       </c>
-      <c r="C53" s="249">
+      <c r="C53" s="179">
         <f>-IE!H41</f>
         <v>-37731.469999999972</v>
       </c>
-      <c r="D53" s="229"/>
+      <c r="D53" s="164"/>
       <c r="E53" s="31"/>
       <c r="F53"/>
       <c r="G53" s="31"/>
@@ -3831,7 +3821,7 @@
       <c r="C54" s="31">
         <v>0</v>
       </c>
-      <c r="D54" s="229">
+      <c r="D54" s="164">
         <f>SUM(C52:C54)</f>
         <v>258927.86</v>
       </c>
@@ -3845,11 +3835,11 @@
         <f>SUM(A12:A54)</f>
         <v>13102128.33</v>
       </c>
-      <c r="B55" s="186" t="s">
+      <c r="B55" s="224" t="s">
         <v>12</v>
       </c>
-      <c r="C55" s="187"/>
-      <c r="D55" s="234">
+      <c r="C55" s="225"/>
+      <c r="D55" s="166">
         <f>SUM(D12:D54)</f>
         <v>12928753.859999999</v>
       </c>
@@ -3857,10 +3847,10 @@
         <f>SUM(E9:E52)</f>
         <v>13102128.33</v>
       </c>
-      <c r="F55" s="186" t="s">
+      <c r="F55" s="224" t="s">
         <v>12</v>
       </c>
-      <c r="G55" s="187"/>
+      <c r="G55" s="225"/>
       <c r="H55" s="94">
         <f>SUM(H8:H53)</f>
         <v>12928753.859999999</v>
@@ -3893,12 +3883,12 @@
       <c r="B58" s="120"/>
       <c r="C58" s="120"/>
       <c r="D58" s="125"/>
-      <c r="E58" s="194" t="s">
+      <c r="E58" s="183" t="s">
         <v>423</v>
       </c>
-      <c r="F58" s="194"/>
-      <c r="G58" s="194"/>
-      <c r="H58" s="195"/>
+      <c r="F58" s="183"/>
+      <c r="G58" s="183"/>
+      <c r="H58" s="184"/>
     </row>
     <row r="59" spans="1:10" s="25" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="119"/>
@@ -3958,12 +3948,12 @@
       <c r="B63" s="130"/>
       <c r="C63" s="131"/>
       <c r="D63" s="125"/>
-      <c r="E63" s="169" t="s">
+      <c r="E63" s="185" t="s">
         <v>426</v>
       </c>
-      <c r="F63" s="169"/>
-      <c r="G63" s="169"/>
-      <c r="H63" s="170"/>
+      <c r="F63" s="185"/>
+      <c r="G63" s="185"/>
+      <c r="H63" s="186"/>
     </row>
     <row r="64" spans="1:10" s="25" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="132" t="s">
@@ -3978,11 +3968,11 @@
       <c r="H64" s="133"/>
     </row>
     <row r="65" spans="1:8" s="25" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="171">
+      <c r="A65" s="181">
         <v>46221</v>
       </c>
-      <c r="B65" s="172"/>
-      <c r="C65" s="172"/>
+      <c r="B65" s="182"/>
+      <c r="C65" s="182"/>
       <c r="D65" s="134"/>
       <c r="E65" s="135"/>
       <c r="F65" s="136"/>
@@ -4048,7 +4038,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.39370078740157483" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
-  <pageSetup paperSize="9" scale="63" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="60" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -4073,52 +4063,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="196" t="s">
+      <c r="A1" s="187" t="s">
         <v>138</v>
       </c>
-      <c r="B1" s="197"/>
-      <c r="C1" s="197"/>
-      <c r="D1" s="197"/>
-      <c r="E1" s="197"/>
-      <c r="F1" s="197"/>
-      <c r="G1" s="197"/>
-      <c r="H1" s="198"/>
+      <c r="B1" s="188"/>
+      <c r="C1" s="188"/>
+      <c r="D1" s="188"/>
+      <c r="E1" s="188"/>
+      <c r="F1" s="188"/>
+      <c r="G1" s="188"/>
+      <c r="H1" s="189"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="199" t="s">
+      <c r="A2" s="190" t="s">
         <v>148</v>
       </c>
-      <c r="B2" s="200"/>
-      <c r="C2" s="200"/>
-      <c r="D2" s="200"/>
-      <c r="E2" s="200"/>
-      <c r="F2" s="200"/>
-      <c r="G2" s="200"/>
-      <c r="H2" s="201"/>
+      <c r="B2" s="191"/>
+      <c r="C2" s="191"/>
+      <c r="D2" s="191"/>
+      <c r="E2" s="191"/>
+      <c r="F2" s="191"/>
+      <c r="G2" s="191"/>
+      <c r="H2" s="192"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="191" t="s">
+      <c r="A3" s="206" t="s">
         <v>186</v>
       </c>
-      <c r="B3" s="192"/>
-      <c r="C3" s="192"/>
-      <c r="D3" s="192"/>
-      <c r="E3" s="192"/>
-      <c r="F3" s="192"/>
-      <c r="G3" s="192"/>
-      <c r="H3" s="193"/>
+      <c r="B3" s="207"/>
+      <c r="C3" s="207"/>
+      <c r="D3" s="207"/>
+      <c r="E3" s="207"/>
+      <c r="F3" s="207"/>
+      <c r="G3" s="207"/>
+      <c r="H3" s="208"/>
     </row>
     <row r="4" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="202" t="s">
+      <c r="A4" s="193" t="s">
         <v>292</v>
       </c>
-      <c r="B4" s="203"/>
-      <c r="C4" s="203"/>
-      <c r="D4" s="203"/>
-      <c r="E4" s="203"/>
-      <c r="F4" s="203"/>
-      <c r="G4" s="203"/>
-      <c r="H4" s="204"/>
+      <c r="B4" s="194"/>
+      <c r="C4" s="194"/>
+      <c r="D4" s="194"/>
+      <c r="E4" s="194"/>
+      <c r="F4" s="194"/>
+      <c r="G4" s="194"/>
+      <c r="H4" s="195"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="142"/>
@@ -4133,24 +4123,24 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="235" t="s">
+      <c r="A6" s="167" t="s">
         <v>218</v>
       </c>
-      <c r="B6" s="236" t="s">
+      <c r="B6" s="198" t="s">
         <v>139</v>
       </c>
-      <c r="C6" s="237"/>
-      <c r="D6" s="238" t="s">
+      <c r="C6" s="199"/>
+      <c r="D6" s="168" t="s">
         <v>293</v>
       </c>
       <c r="E6" s="141" t="str">
         <f>A6</f>
         <v>2024-2025</v>
       </c>
-      <c r="F6" s="207" t="s">
+      <c r="F6" s="200" t="s">
         <v>48</v>
       </c>
-      <c r="G6" s="208"/>
+      <c r="G6" s="201"/>
       <c r="H6" s="141" t="str">
         <f>D6</f>
         <v>2025-2026</v>
@@ -4163,12 +4153,12 @@
         <v>209</v>
       </c>
       <c r="C7" s="38"/>
-      <c r="D7" s="239"/>
+      <c r="D7" s="169"/>
       <c r="E7" s="38"/>
-      <c r="F7" s="209" t="s">
+      <c r="F7" s="202" t="s">
         <v>166</v>
       </c>
-      <c r="G7" s="210"/>
+      <c r="G7" s="203"/>
       <c r="H7" s="38"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -4181,7 +4171,7 @@
       <c r="C8" s="37">
         <v>43200</v>
       </c>
-      <c r="D8" s="240"/>
+      <c r="D8" s="170"/>
       <c r="E8" s="37">
         <v>55068</v>
       </c>
@@ -4203,7 +4193,7 @@
       <c r="C9" s="39">
         <v>4800</v>
       </c>
-      <c r="D9" s="241">
+      <c r="D9" s="171">
         <f>SUM(C8:C9)</f>
         <v>48000</v>
       </c>
@@ -4222,7 +4212,7 @@
       <c r="A10" s="156"/>
       <c r="B10" s="32"/>
       <c r="C10" s="40"/>
-      <c r="D10" s="242"/>
+      <c r="D10" s="172"/>
       <c r="E10" s="37">
         <v>0</v>
       </c>
@@ -4242,7 +4232,7 @@
         <v>141</v>
       </c>
       <c r="C11" s="37"/>
-      <c r="D11" s="242">
+      <c r="D11" s="172">
         <v>118050</v>
       </c>
       <c r="E11" s="37">
@@ -4265,7 +4255,7 @@
         <v>142</v>
       </c>
       <c r="C12" s="37"/>
-      <c r="D12" s="242">
+      <c r="D12" s="172">
         <v>63958</v>
       </c>
       <c r="E12" s="37">
@@ -4283,7 +4273,7 @@
       <c r="A13" s="156"/>
       <c r="B13" s="32"/>
       <c r="C13" s="40"/>
-      <c r="D13" s="243"/>
+      <c r="D13" s="173"/>
       <c r="E13" s="37">
         <v>5249</v>
       </c>
@@ -4301,7 +4291,7 @@
         <v>210</v>
       </c>
       <c r="C14" s="38"/>
-      <c r="D14" s="239"/>
+      <c r="D14" s="169"/>
       <c r="E14" s="37">
         <v>192504</v>
       </c>
@@ -4326,7 +4316,7 @@
       <c r="C15" s="37">
         <v>31915</v>
       </c>
-      <c r="D15" s="244">
+      <c r="D15" s="174">
         <f>SUM(C15)</f>
         <v>31915</v>
       </c>
@@ -4341,7 +4331,7 @@
         <v>211</v>
       </c>
       <c r="C16" s="41"/>
-      <c r="D16" s="241"/>
+      <c r="D16" s="171"/>
       <c r="E16" s="38"/>
       <c r="F16" s="36" t="s">
         <v>167</v>
@@ -4359,7 +4349,7 @@
       <c r="C17" s="100">
         <v>10000</v>
       </c>
-      <c r="D17" s="245"/>
+      <c r="D17" s="175"/>
       <c r="E17" s="41">
         <v>99936</v>
       </c>
@@ -4382,7 +4372,7 @@
       <c r="C18" s="39">
         <v>143500</v>
       </c>
-      <c r="D18" s="246">
+      <c r="D18" s="176">
         <f>C17+C18</f>
         <v>153500</v>
       </c>
@@ -4406,7 +4396,7 @@
         <v>213</v>
       </c>
       <c r="C19" s="54"/>
-      <c r="D19" s="246"/>
+      <c r="D19" s="176"/>
       <c r="E19" s="40"/>
       <c r="F19" s="32"/>
       <c r="G19" s="40"/>
@@ -4422,7 +4412,7 @@
       <c r="C20" s="54">
         <v>1650</v>
       </c>
-      <c r="D20" s="246"/>
+      <c r="D20" s="176"/>
       <c r="E20" s="38"/>
       <c r="F20" s="36" t="s">
         <v>140</v>
@@ -4440,7 +4430,7 @@
       <c r="C21" s="54">
         <v>5785</v>
       </c>
-      <c r="D21" s="246"/>
+      <c r="D21" s="176"/>
       <c r="E21" s="41">
         <v>15420</v>
       </c>
@@ -4462,7 +4452,7 @@
       <c r="C22" s="54">
         <v>58285</v>
       </c>
-      <c r="D22" s="246"/>
+      <c r="D22" s="176"/>
       <c r="E22" s="41"/>
       <c r="F22" s="36"/>
       <c r="G22" s="37"/>
@@ -4478,7 +4468,7 @@
       <c r="C23" s="54">
         <v>7200</v>
       </c>
-      <c r="D23" s="247"/>
+      <c r="D23" s="177"/>
       <c r="E23" s="41">
         <v>108834</v>
       </c>
@@ -4501,7 +4491,7 @@
       <c r="C24" s="54">
         <v>20650</v>
       </c>
-      <c r="D24" s="247"/>
+      <c r="D24" s="177"/>
       <c r="E24" s="41"/>
       <c r="F24" s="52" t="s">
         <v>131</v>
@@ -4519,7 +4509,7 @@
       <c r="C25" s="54">
         <v>1390</v>
       </c>
-      <c r="D25" s="247"/>
+      <c r="D25" s="177"/>
       <c r="E25" s="41">
         <v>-10365</v>
       </c>
@@ -4542,7 +4532,7 @@
       <c r="C26" s="39">
         <v>0</v>
       </c>
-      <c r="D26" s="247">
+      <c r="D26" s="177">
         <f>SUM(C20:C26)</f>
         <v>94960</v>
       </c>
@@ -4564,7 +4554,7 @@
         <v>217</v>
       </c>
       <c r="C27" s="38"/>
-      <c r="D27" s="239"/>
+      <c r="D27" s="169"/>
       <c r="E27" s="41">
         <v>-36300</v>
       </c>
@@ -4587,7 +4577,7 @@
       <c r="C28" s="37">
         <v>9096</v>
       </c>
-      <c r="D28" s="241"/>
+      <c r="D28" s="171"/>
       <c r="E28" s="41">
         <v>-19352</v>
       </c>
@@ -4610,7 +4600,7 @@
       <c r="C29" s="37">
         <v>4900</v>
       </c>
-      <c r="D29" s="241"/>
+      <c r="D29" s="171"/>
       <c r="E29" s="6">
         <v>-1075</v>
       </c>
@@ -4636,7 +4626,7 @@
       <c r="C30" s="37">
         <v>2500</v>
       </c>
-      <c r="D30" s="241"/>
+      <c r="D30" s="171"/>
       <c r="E30" s="42"/>
       <c r="F30" s="6"/>
       <c r="G30" s="42"/>
@@ -4652,7 +4642,7 @@
       <c r="C31" s="39">
         <v>826</v>
       </c>
-      <c r="D31" s="241">
+      <c r="D31" s="171">
         <f>SUM(C28:C31)</f>
         <v>17322</v>
       </c>
@@ -4673,7 +4663,7 @@
         <v>216</v>
       </c>
       <c r="C32" s="38"/>
-      <c r="D32" s="239"/>
+      <c r="D32" s="169"/>
       <c r="E32" s="42"/>
       <c r="F32" s="6"/>
       <c r="G32" s="42"/>
@@ -4689,7 +4679,7 @@
       <c r="C33" s="37">
         <v>0</v>
       </c>
-      <c r="D33" s="241"/>
+      <c r="D33" s="171"/>
       <c r="E33" s="38"/>
       <c r="F33" s="36" t="s">
         <v>215</v>
@@ -4707,7 +4697,7 @@
       <c r="C34" s="37">
         <v>226</v>
       </c>
-      <c r="D34" s="241"/>
+      <c r="D34" s="171"/>
       <c r="E34" s="41">
         <v>0</v>
       </c>
@@ -4729,7 +4719,7 @@
       <c r="C35" s="37">
         <v>2208</v>
       </c>
-      <c r="D35" s="241"/>
+      <c r="D35" s="171"/>
       <c r="E35" s="41">
         <v>5000</v>
       </c>
@@ -4754,7 +4744,7 @@
       <c r="C36" s="37">
         <v>140.47</v>
       </c>
-      <c r="D36" s="241"/>
+      <c r="D36" s="171"/>
       <c r="E36" s="41"/>
       <c r="F36" s="32"/>
       <c r="G36" s="37"/>
@@ -4770,10 +4760,10 @@
       <c r="C37" s="37">
         <v>100</v>
       </c>
-      <c r="D37" s="241"/>
+      <c r="D37" s="171"/>
       <c r="E37" s="40"/>
-      <c r="F37" s="211"/>
-      <c r="G37" s="212"/>
+      <c r="F37" s="204"/>
+      <c r="G37" s="205"/>
       <c r="H37" s="157"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
@@ -4786,7 +4776,7 @@
       <c r="C38" s="37">
         <v>150</v>
       </c>
-      <c r="D38" s="241"/>
+      <c r="D38" s="171"/>
       <c r="E38" s="40"/>
       <c r="F38" s="83"/>
       <c r="G38" s="118"/>
@@ -4802,7 +4792,7 @@
       <c r="C39" s="39">
         <v>3431</v>
       </c>
-      <c r="D39" s="241">
+      <c r="D39" s="171">
         <f>SUM(C33:C39)</f>
         <v>6255.4699999999993</v>
       </c>
@@ -4815,7 +4805,7 @@
       <c r="A40" s="154"/>
       <c r="B40" s="88"/>
       <c r="C40" s="37"/>
-      <c r="D40" s="241"/>
+      <c r="D40" s="171"/>
       <c r="E40" s="42"/>
       <c r="F40" s="6"/>
       <c r="G40" s="42"/>
@@ -4829,7 +4819,7 @@
         <v>143</v>
       </c>
       <c r="C41" s="40"/>
-      <c r="D41" s="242">
+      <c r="D41" s="172">
         <v>0</v>
       </c>
       <c r="E41" s="42">
@@ -4852,7 +4842,7 @@
         <v>188</v>
       </c>
       <c r="C42" s="99"/>
-      <c r="D42" s="242">
+      <c r="D42" s="172">
         <v>0</v>
       </c>
       <c r="E42" s="42"/>
@@ -4865,11 +4855,11 @@
         <f>SUM(A8:A42)</f>
         <v>418178</v>
       </c>
-      <c r="B43" s="205" t="s">
+      <c r="B43" s="196" t="s">
         <v>12</v>
       </c>
-      <c r="C43" s="206"/>
-      <c r="D43" s="248">
+      <c r="C43" s="197"/>
+      <c r="D43" s="178">
         <f>SUM(D8:D42)</f>
         <v>533960.47</v>
       </c>
@@ -4877,10 +4867,10 @@
         <f>SUM(E8:E41)</f>
         <v>418178</v>
       </c>
-      <c r="F43" s="205" t="s">
+      <c r="F43" s="196" t="s">
         <v>12</v>
       </c>
-      <c r="G43" s="206"/>
+      <c r="G43" s="197"/>
       <c r="H43" s="103">
         <f>SUM(H8:H41)</f>
         <v>533960.47</v>
@@ -4924,12 +4914,12 @@
       <c r="B46" s="120"/>
       <c r="C46" s="120"/>
       <c r="D46" s="125"/>
-      <c r="E46" s="194" t="s">
+      <c r="E46" s="183" t="s">
         <v>423</v>
       </c>
-      <c r="F46" s="194"/>
-      <c r="G46" s="194"/>
-      <c r="H46" s="195"/>
+      <c r="F46" s="183"/>
+      <c r="G46" s="183"/>
+      <c r="H46" s="184"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="119"/>
@@ -4980,12 +4970,12 @@
       <c r="B51" s="130"/>
       <c r="C51" s="131"/>
       <c r="D51" s="125"/>
-      <c r="E51" s="169" t="s">
+      <c r="E51" s="185" t="s">
         <v>426</v>
       </c>
-      <c r="F51" s="169"/>
-      <c r="G51" s="169"/>
-      <c r="H51" s="170"/>
+      <c r="F51" s="185"/>
+      <c r="G51" s="185"/>
+      <c r="H51" s="186"/>
     </row>
     <row r="52" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="132" t="s">
@@ -5000,11 +4990,11 @@
       <c r="H52" s="133"/>
     </row>
     <row r="53" spans="1:10" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="171">
+      <c r="A53" s="181">
         <v>46215</v>
       </c>
-      <c r="B53" s="172"/>
-      <c r="C53" s="172"/>
+      <c r="B53" s="182"/>
+      <c r="C53" s="182"/>
       <c r="D53" s="134"/>
       <c r="E53" s="135"/>
       <c r="F53" s="136"/>
@@ -5060,35 +5050,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.35">
-      <c r="B1" s="213" t="str">
+      <c r="B1" s="232" t="str">
         <f>+IE!A1</f>
         <v>KITTY PARK CO-OP. HOUSING SOCIETY LTD.</v>
       </c>
-      <c r="C1" s="213"/>
-      <c r="D1" s="213"/>
-      <c r="E1" s="213"/>
-      <c r="F1" s="213"/>
-      <c r="G1" s="213"/>
-      <c r="H1" s="213"/>
-      <c r="I1" s="213"/>
-      <c r="J1" s="213"/>
-      <c r="K1" s="213"/>
-      <c r="L1" s="213"/>
+      <c r="C1" s="232"/>
+      <c r="D1" s="232"/>
+      <c r="E1" s="232"/>
+      <c r="F1" s="232"/>
+      <c r="G1" s="232"/>
+      <c r="H1" s="232"/>
+      <c r="I1" s="232"/>
+      <c r="J1" s="232"/>
+      <c r="K1" s="232"/>
+      <c r="L1" s="232"/>
     </row>
     <row r="2" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B2" s="214" t="s">
+      <c r="B2" s="233" t="s">
         <v>294</v>
       </c>
-      <c r="C2" s="214"/>
-      <c r="D2" s="214"/>
-      <c r="E2" s="214"/>
-      <c r="F2" s="214"/>
-      <c r="G2" s="214"/>
-      <c r="H2" s="214"/>
-      <c r="I2" s="214"/>
-      <c r="J2" s="214"/>
-      <c r="K2" s="214"/>
-      <c r="L2" s="214"/>
+      <c r="C2" s="233"/>
+      <c r="D2" s="233"/>
+      <c r="E2" s="233"/>
+      <c r="F2" s="233"/>
+      <c r="G2" s="233"/>
+      <c r="H2" s="233"/>
+      <c r="I2" s="233"/>
+      <c r="J2" s="233"/>
+      <c r="K2" s="233"/>
+      <c r="L2" s="233"/>
     </row>
     <row r="3" spans="1:12" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="104" t="s">
@@ -6303,10 +6293,10 @@
     </row>
     <row r="42" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="107"/>
-      <c r="B42" s="167" t="s">
+      <c r="B42" s="234" t="s">
         <v>194</v>
       </c>
-      <c r="C42" s="168"/>
+      <c r="C42" s="235"/>
       <c r="D42" s="110">
         <f>D14+D19+D22+D29+D36+D40</f>
         <v>1318170</v>
@@ -6341,9 +6331,9 @@
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C44" s="109"/>
       <c r="D44" s="109"/>
-      <c r="I44" s="215"/>
-      <c r="J44" s="215"/>
-      <c r="K44" s="215"/>
+      <c r="I44" s="236"/>
+      <c r="J44" s="236"/>
+      <c r="K44" s="236"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B45" s="10"/>
@@ -6439,20 +6429,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="164" t="s">
+      <c r="A1" s="237" t="s">
         <v>203</v>
       </c>
-      <c r="B1" s="164"/>
-      <c r="C1" s="164"/>
-      <c r="D1" s="164"/>
+      <c r="B1" s="237"/>
+      <c r="C1" s="237"/>
+      <c r="D1" s="237"/>
     </row>
     <row r="2" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="165" t="s">
+      <c r="A2" s="240" t="s">
         <v>418</v>
       </c>
-      <c r="B2" s="165"/>
-      <c r="C2" s="165"/>
-      <c r="D2" s="165"/>
+      <c r="B2" s="240"/>
+      <c r="C2" s="240"/>
+      <c r="D2" s="240"/>
     </row>
     <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="50" t="s">
@@ -6483,11 +6473,11 @@
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="166" t="s">
+      <c r="A5" s="239" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="167"/>
-      <c r="C5" s="168"/>
+      <c r="B5" s="234"/>
+      <c r="C5" s="235"/>
       <c r="D5" s="57">
         <f>SUM(D4:D4)</f>
         <v>20965</v>
@@ -6495,12 +6485,12 @@
     </row>
     <row r="6" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="165" t="s">
+      <c r="A8" s="240" t="s">
         <v>417</v>
       </c>
-      <c r="B8" s="165"/>
-      <c r="C8" s="165"/>
-      <c r="D8" s="165"/>
+      <c r="B8" s="240"/>
+      <c r="C8" s="240"/>
+      <c r="D8" s="240"/>
     </row>
     <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="50" t="s">
@@ -6559,11 +6549,11 @@
       </c>
     </row>
     <row r="13" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="166" t="s">
+      <c r="A13" s="239" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="167"/>
-      <c r="C13" s="168"/>
+      <c r="B13" s="234"/>
+      <c r="C13" s="235"/>
       <c r="D13" s="57">
         <f>SUM(D10:D12)</f>
         <v>78327</v>
@@ -6574,20 +6564,20 @@
       <c r="D14" s="59"/>
     </row>
     <row r="15" spans="1:4" ht="18" x14ac:dyDescent="0.3">
-      <c r="A15" s="164" t="s">
+      <c r="A15" s="237" t="s">
         <v>203</v>
       </c>
-      <c r="B15" s="164"/>
-      <c r="C15" s="164"/>
-      <c r="D15" s="164"/>
+      <c r="B15" s="237"/>
+      <c r="C15" s="237"/>
+      <c r="D15" s="237"/>
     </row>
     <row r="16" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="216" t="s">
+      <c r="A16" s="238" t="s">
         <v>402</v>
       </c>
-      <c r="B16" s="216"/>
-      <c r="C16" s="216"/>
-      <c r="D16" s="216"/>
+      <c r="B16" s="238"/>
+      <c r="C16" s="238"/>
+      <c r="D16" s="238"/>
     </row>
     <row r="17" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="50" t="s">
@@ -6816,12 +6806,12 @@
     </row>
     <row r="33" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="35" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="216" t="s">
+      <c r="A35" s="238" t="s">
         <v>420</v>
       </c>
-      <c r="B35" s="216"/>
-      <c r="C35" s="216"/>
-      <c r="D35" s="216"/>
+      <c r="B35" s="238"/>
+      <c r="C35" s="238"/>
+      <c r="D35" s="238"/>
     </row>
     <row r="36" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="50" t="s">
@@ -6950,11 +6940,11 @@
       </c>
     </row>
     <row r="45" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="166" t="s">
+      <c r="A45" s="239" t="s">
         <v>12</v>
       </c>
-      <c r="B45" s="167"/>
-      <c r="C45" s="168"/>
+      <c r="B45" s="234"/>
+      <c r="C45" s="235"/>
       <c r="D45" s="67">
         <f>SUM(D37:D44)</f>
         <v>259403.75</v>
@@ -6997,20 +6987,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="164" t="s">
+      <c r="A1" s="237" t="s">
         <v>203</v>
       </c>
-      <c r="B1" s="164"/>
-      <c r="C1" s="164"/>
-      <c r="D1" s="164"/>
+      <c r="B1" s="237"/>
+      <c r="C1" s="237"/>
+      <c r="D1" s="237"/>
     </row>
     <row r="2" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="216" t="s">
+      <c r="A2" s="238" t="s">
         <v>402</v>
       </c>
-      <c r="B2" s="216"/>
-      <c r="C2" s="216"/>
-      <c r="D2" s="216"/>
+      <c r="B2" s="238"/>
+      <c r="C2" s="238"/>
+      <c r="D2" s="238"/>
     </row>
     <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="50" t="s">
@@ -7250,12 +7240,12 @@
       <c r="D20" s="58"/>
     </row>
     <row r="21" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="216" t="s">
+      <c r="A21" s="238" t="s">
         <v>420</v>
       </c>
-      <c r="B21" s="216"/>
-      <c r="C21" s="216"/>
-      <c r="D21" s="216"/>
+      <c r="B21" s="238"/>
+      <c r="C21" s="238"/>
+      <c r="D21" s="238"/>
     </row>
     <row r="22" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="50" t="s">
@@ -7384,11 +7374,11 @@
       </c>
     </row>
     <row r="31" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="166" t="s">
+      <c r="A31" s="239" t="s">
         <v>12</v>
       </c>
-      <c r="B31" s="167"/>
-      <c r="C31" s="168"/>
+      <c r="B31" s="234"/>
+      <c r="C31" s="235"/>
       <c r="D31" s="67">
         <f>SUM(D23:D30)</f>
         <v>259403.75</v>
@@ -7424,12 +7414,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="217" t="s">
+      <c r="A1" s="241" t="s">
         <v>117</v>
       </c>
-      <c r="B1" s="218"/>
-      <c r="C1" s="218"/>
-      <c r="D1" s="218"/>
+      <c r="B1" s="242"/>
+      <c r="C1" s="242"/>
+      <c r="D1" s="242"/>
       <c r="E1" s="16"/>
       <c r="F1" s="17"/>
       <c r="G1" s="17"/>
@@ -7444,12 +7434,12 @@
       <c r="P1" s="17"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" s="219" t="s">
+      <c r="A2" s="243" t="s">
         <v>421</v>
       </c>
-      <c r="B2" s="220"/>
-      <c r="C2" s="220"/>
-      <c r="D2" s="220"/>
+      <c r="B2" s="244"/>
+      <c r="C2" s="244"/>
+      <c r="D2" s="244"/>
       <c r="E2" s="17"/>
       <c r="F2" s="17"/>
       <c r="G2" s="17"/>
@@ -7711,12 +7701,12 @@
       <c r="P12" s="17"/>
     </row>
     <row r="13" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="217" t="s">
+      <c r="A13" s="241" t="s">
         <v>117</v>
       </c>
-      <c r="B13" s="218"/>
-      <c r="C13" s="218"/>
-      <c r="D13" s="218"/>
+      <c r="B13" s="242"/>
+      <c r="C13" s="242"/>
+      <c r="D13" s="242"/>
       <c r="E13" s="17"/>
       <c r="F13" s="17"/>
       <c r="G13" s="17"/>
@@ -7731,12 +7721,12 @@
       <c r="P13" s="17"/>
     </row>
     <row r="14" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="219" t="s">
+      <c r="A14" s="243" t="s">
         <v>422</v>
       </c>
-      <c r="B14" s="220"/>
-      <c r="C14" s="220"/>
-      <c r="D14" s="220"/>
+      <c r="B14" s="244"/>
+      <c r="C14" s="244"/>
+      <c r="D14" s="244"/>
       <c r="E14" s="17"/>
       <c r="F14" s="17"/>
       <c r="G14" s="17"/>
@@ -24866,12 +24856,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="221" t="s">
+      <c r="A1" s="245" t="s">
         <v>229</v>
       </c>
-      <c r="B1" s="222"/>
-      <c r="C1" s="222"/>
-      <c r="D1" s="222"/>
+      <c r="B1" s="246"/>
+      <c r="C1" s="246"/>
+      <c r="D1" s="246"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="71" t="s">
@@ -25952,10 +25942,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="221" t="s">
+      <c r="A2" s="245" t="s">
         <v>250</v>
       </c>
-      <c r="B2" s="221"/>
+      <c r="B2" s="245"/>
       <c r="C2" t="s">
         <v>249</v>
       </c>
@@ -26003,10 +25993,10 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="221" t="s">
+      <c r="A8" s="245" t="s">
         <v>250</v>
       </c>
-      <c r="B8" s="221"/>
+      <c r="B8" s="245"/>
       <c r="C8" t="s">
         <v>249</v>
       </c>
@@ -26069,26 +26059,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="221" t="s">
+      <c r="A1" s="245" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="221"/>
-      <c r="C1" s="221"/>
-      <c r="D1" s="221"/>
-      <c r="E1" s="221"/>
-      <c r="F1" s="221"/>
-      <c r="G1" s="221"/>
+      <c r="B1" s="245"/>
+      <c r="C1" s="245"/>
+      <c r="D1" s="245"/>
+      <c r="E1" s="245"/>
+      <c r="F1" s="245"/>
+      <c r="G1" s="245"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="221" t="s">
+      <c r="A2" s="245" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="221"/>
-      <c r="C2" s="221"/>
-      <c r="D2" s="221"/>
-      <c r="E2" s="221"/>
-      <c r="F2" s="221"/>
-      <c r="G2" s="221"/>
+      <c r="B2" s="245"/>
+      <c r="C2" s="245"/>
+      <c r="D2" s="245"/>
+      <c r="E2" s="245"/>
+      <c r="F2" s="245"/>
+      <c r="G2" s="245"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
